--- a/excel/Control_Total_Planta.xlsx
+++ b/excel/Control_Total_Planta.xlsx
@@ -16,7 +16,7 @@
     <sheet name="RESIDUOS_PRODUCCION" sheetId="7" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'INVENTARIO'!$A$1:$S$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'INVENTARIO'!$A$1:$S$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'PRODUCCION'!$A$1:$N$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'DESPACHO'!$A$1:$L$4</definedName>
   </definedNames>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="132">
   <si>
     <t>DASHBOARD CONTROL PLANTA</t>
   </si>
@@ -262,6 +262,21 @@
   </si>
   <si>
     <t>2026-05-07 21:32:20</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>11:33</t>
+  </si>
+  <si>
+    <t>Comercio</t>
+  </si>
+  <si>
+    <t>AFO-20260508-1</t>
+  </si>
+  <si>
+    <t>2026-05-08 18:35:58</t>
   </si>
   <si>
     <t>puerto</t>
@@ -829,7 +844,7 @@
       </c>
       <c r="B3" s="1">
         <f>SUM(INVENTARIO!P:P)</f>
-        <v>2300</v>
+        <v>2799.98000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -863,7 +878,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S8"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="8.141" bestFit="true" customWidth="true" style="0"/>
@@ -1300,9 +1315,68 @@
         <v>78</v>
       </c>
     </row>
+    <row r="8" spans="1:19">
+      <c r="A8" s="8">
+        <v>1</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="8">
+        <v>232323</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="P8" s="10">
+        <v>499.98000000000002</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>123123</v>
+      </c>
+      <c r="R8" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="S8" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection password="D97C" sheet="1" sort="1" autoFilter="1"/>
-  <autoFilter ref="A1:S7"/>
+  <autoFilter ref="A1:S8"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
@@ -1355,10 +1429,10 @@
         <v>21</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1366,7 +1440,7 @@
         <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
@@ -1390,7 +1464,7 @@
         <v>2</v>
       </c>
       <c r="J2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -1398,7 +1472,7 @@
         <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
         <v>42</v>
@@ -1422,7 +1496,7 @@
         <v>2</v>
       </c>
       <c r="J3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -1430,7 +1504,7 @@
         <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
         <v>62</v>
@@ -1454,7 +1528,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1493,16 +1567,16 @@
         <v>4</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>6</v>
@@ -1511,13 +1585,13 @@
         <v>14</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>16</v>
@@ -1526,10 +1600,10 @@
         <v>19</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -1540,40 +1614,40 @@
         <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D2" s="3">
         <v>2</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H2" s="3">
         <v>2</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J2" s="3">
         <v>1</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L2" s="5">
         <v>100.0</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -1584,31 +1658,31 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H3">
         <v>1</v>
       </c>
       <c r="I3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="L3" s="7">
         <v>100.0</v>
@@ -1617,7 +1691,7 @@
         <v>1</v>
       </c>
       <c r="N3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -1628,38 +1702,38 @@
         <v>60</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D4" s="8">
         <v>2</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="H4" s="8">
         <v>1</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="L4" s="10">
         <v>50.0</v>
       </c>
       <c r="M4" s="8"/>
       <c r="N4" s="8" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1701,34 +1775,34 @@
         <v>5</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>14</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -1739,34 +1813,34 @@
         <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D2" s="3">
         <v>111</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G2" s="5">
         <v>100.0</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="K2" s="3">
         <v>1</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1783,19 +1857,19 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="F3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G3" s="7">
         <v>100.0</v>
       </c>
       <c r="H3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -1804,7 +1878,7 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1815,32 +1889,32 @@
         <v>60</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D4" s="8">
         <v>101</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G4" s="10">
         <v>50.0</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="K4" s="8"/>
       <c r="L4" s="8" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1880,13 +1954,13 @@
         <v>4</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>10</v>
@@ -1904,7 +1978,7 @@
         <v>18</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>9</v>
@@ -1949,19 +2023,19 @@
         <v>6</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>19</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>22</v>
